--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554410.228219559</v>
+        <v>554410</v>
       </c>
       <c r="R2" t="n">
-        <v>6262723.825087707</v>
+        <v>6262724</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75016697</v>
       </c>
       <c r="B2" t="n">
-        <v>103181</v>
+        <v>103191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8311-2024 artfynd.xlsx
+++ b/artfynd/A 8311-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75016697</v>
+        <v>63188725</v>
       </c>
       <c r="B2" t="n">
-        <v>103191</v>
+        <v>56816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222002</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>L5 Skräplemo 1400 m OSO, Sm</t>
+          <t>Harstensbo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554410</v>
+        <v>554385</v>
       </c>
       <c r="R2" t="n">
-        <v>6262724</v>
+        <v>6262834</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +764,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2010-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
+          <t>2010-06-21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G2a 4248. SOM: Viola mirabilis. LEG: Bengt Lundgren</t>
+          <t>Box-ID: 22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,23 +786,125 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lund</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>75016697</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103682</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L5 Skräplemo 1400 m OSO, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>554410</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6262724</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 4G2a 4248. SOM: Viola mirabilis. LEG: Bengt Lundgren</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
